--- a/Data/ClientOpening.xlsx
+++ b/Data/ClientOpening.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:101_{0413D050-21F2-4717-9F76-C04B6C41AFE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A110C571-64B7-482A-96DE-91F27FD44511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" tabRatio="763" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="56">
   <si>
     <t>clientid_Num</t>
   </si>
@@ -181,13 +181,25 @@
   </si>
   <si>
     <t>cm_ID</t>
+  </si>
+  <si>
+    <t>netWorth</t>
+  </si>
+  <si>
+    <t>c10092040</t>
+  </si>
+  <si>
+    <t>TMCM_Linking_CM_42</t>
+  </si>
+  <si>
+    <t>TM_CM_Linking_TM_42</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,6 +247,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -289,7 +308,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -687,10 +706,12 @@
       <c r="AB1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="AC1" s="9" t="s">
+      <c r="AC1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="AD1" s="1"/>
+      <c r="AD1" s="9" t="s">
+        <v>52</v>
+      </c>
       <c r="AE1" s="1"/>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
@@ -778,13 +799,13 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
-        <v>101</v>
+        <v>9012</v>
       </c>
       <c r="B3" s="6">
         <v>6421</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>42</v>
@@ -862,20 +883,22 @@
         <v>49</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD3" s="1"/>
+        <v>53</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>5</v>
+      </c>
       <c r="AE3" s="1"/>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
-        <v>9092</v>
+        <v>90921</v>
       </c>
       <c r="B4" s="6">
         <v>3216</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>43</v>
@@ -943,11 +966,21 @@
       <c r="Y4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
+      <c r="Z4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>5</v>
+      </c>
       <c r="AE4" s="1"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">

--- a/Data/ClientOpening.xlsx
+++ b/Data/ClientOpening.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A110C571-64B7-482A-96DE-91F27FD44511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F5E1FA-9D7D-45BA-97A0-118C0E0A11A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" tabRatio="763" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="68">
   <si>
     <t>clientid_Num</t>
   </si>
@@ -193,6 +193,42 @@
   </si>
   <si>
     <t>TM_CM_Linking_TM_42</t>
+  </si>
+  <si>
+    <t>nominee_name</t>
+  </si>
+  <si>
+    <t>nominee_pan_no</t>
+  </si>
+  <si>
+    <t>nominee_address</t>
+  </si>
+  <si>
+    <t>nominee_relation</t>
+  </si>
+  <si>
+    <t>nominee_years</t>
+  </si>
+  <si>
+    <t>nominee_Date</t>
+  </si>
+  <si>
+    <t>abhishek</t>
+  </si>
+  <si>
+    <t>BPTPT1234H</t>
+  </si>
+  <si>
+    <t>vasai</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>nominee_Month+1</t>
   </si>
 </sst>
 </file>
@@ -208,12 +244,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
       <b/>
       <i/>
       <sz val="10"/>
@@ -225,12 +255,6 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF2A00FF"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -254,6 +278,23 @@
       <color rgb="FF000000"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -296,19 +337,18 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -590,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AL9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -619,787 +659,885 @@
     <col min="26" max="26" width="14.28515625" customWidth="1"/>
     <col min="27" max="27" width="12.28515625" customWidth="1"/>
     <col min="28" max="28" width="13.42578125" customWidth="1"/>
+    <col min="31" max="31" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="35" width="15.140625" customWidth="1"/>
+    <col min="36" max="36" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="Z1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AA1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AB1" s="7" t="s">
+      <c r="AB1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AC1" s="7" t="s">
+      <c r="AC1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="AD1" s="9" t="s">
+      <c r="AD1" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AE1" s="1"/>
+      <c r="AE1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG1" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AH1" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AI1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AK1" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AL1" s="5"/>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
-        <v>9090</v>
-      </c>
-      <c r="B2" s="6">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>9190</v>
+      </c>
+      <c r="B2" s="3">
         <v>3214</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="3">
+        <v>401202</v>
+      </c>
+      <c r="N2" s="3">
+        <v>91</v>
+      </c>
+      <c r="O2" s="3">
+        <v>9730150615</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>9696696</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5">
+        <v>5</v>
+      </c>
+      <c r="AE2" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG2" s="5">
+        <v>2007</v>
+      </c>
+      <c r="AH2" s="5">
+        <v>10</v>
+      </c>
+      <c r="AI2" s="5">
+        <v>19</v>
+      </c>
+      <c r="AJ2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL2" s="5"/>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>9012</v>
+      </c>
+      <c r="B3" s="3">
+        <v>6421</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="3">
+        <v>401202</v>
+      </c>
+      <c r="N3" s="3">
+        <v>91</v>
+      </c>
+      <c r="O3" s="3">
+        <v>9730150615</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>9696697</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA3" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB3" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD3" s="5">
+        <v>5</v>
+      </c>
+      <c r="AE3" s="5"/>
+      <c r="AF3" s="5"/>
+      <c r="AG3" s="5"/>
+      <c r="AH3" s="5"/>
+      <c r="AI3" s="5"/>
+      <c r="AJ3" s="5"/>
+      <c r="AK3" s="5"/>
+      <c r="AL3" s="5"/>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A4" s="7">
+        <v>90921</v>
+      </c>
+      <c r="B4" s="3">
+        <v>3216</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="3">
+        <v>401202</v>
+      </c>
+      <c r="N4" s="3">
+        <v>91</v>
+      </c>
+      <c r="O4" s="3">
+        <v>9730150615</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>9696698</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD4" s="5">
+        <v>5</v>
+      </c>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="5"/>
+      <c r="AG4" s="5"/>
+      <c r="AH4" s="5"/>
+      <c r="AI4" s="5"/>
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="5"/>
+      <c r="AL4" s="5"/>
+    </row>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
+        <v>9093</v>
+      </c>
+      <c r="B5" s="3">
+        <v>3217</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M5" s="3">
         <v>401202</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N5" s="3">
         <v>91</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O5" s="3">
         <v>9730150615</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="Q2" s="5">
-        <v>9696696</v>
-      </c>
-      <c r="R2" s="6" t="s">
+      <c r="Q5" s="3">
+        <v>9696699</v>
+      </c>
+      <c r="R5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="S5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="T5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="U5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="V5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="W5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="X5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Y5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
-      <c r="AB2" s="1"/>
-      <c r="AC2" s="1"/>
-      <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
+      <c r="Z5" s="5"/>
+      <c r="AA5" s="5"/>
+      <c r="AB5" s="5"/>
+      <c r="AC5" s="5"/>
+      <c r="AD5" s="5"/>
+      <c r="AE5" s="5"/>
+      <c r="AF5" s="5"/>
+      <c r="AG5" s="5"/>
+      <c r="AH5" s="5"/>
+      <c r="AI5" s="5"/>
+      <c r="AJ5" s="5"/>
+      <c r="AK5" s="5"/>
+      <c r="AL5" s="5"/>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
-        <v>9012</v>
-      </c>
-      <c r="B3" s="6">
-        <v>6421</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="6" t="s">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>9094</v>
+      </c>
+      <c r="B6" s="3">
+        <v>3218</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M6" s="3">
         <v>401202</v>
       </c>
-      <c r="N3" s="5">
+      <c r="N6" s="3">
         <v>91</v>
       </c>
-      <c r="O3" s="5">
+      <c r="O6" s="3">
         <v>9730150615</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="5">
-        <v>9696697</v>
-      </c>
-      <c r="R3" s="6" t="s">
+      <c r="Q6" s="3">
+        <v>9696700</v>
+      </c>
+      <c r="R6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="U6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="V6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="W6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="6" t="s">
+      <c r="X6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="Y6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="Z3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD3" s="1">
-        <v>5</v>
-      </c>
-      <c r="AE3" s="1"/>
+      <c r="Z6" s="5"/>
+      <c r="AA6" s="5"/>
+      <c r="AB6" s="5"/>
+      <c r="AC6" s="5"/>
+      <c r="AD6" s="5"/>
+      <c r="AE6" s="5"/>
+      <c r="AF6" s="5"/>
+      <c r="AG6" s="5"/>
+      <c r="AH6" s="5"/>
+      <c r="AI6" s="5"/>
+      <c r="AJ6" s="5"/>
+      <c r="AK6" s="5"/>
+      <c r="AL6" s="5"/>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
-        <v>90921</v>
-      </c>
-      <c r="B4" s="6">
-        <v>3216</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="6" t="s">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>9095</v>
+      </c>
+      <c r="B7" s="3">
+        <v>3219</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M7" s="3">
         <v>401202</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N7" s="3">
         <v>91</v>
       </c>
-      <c r="O4" s="5">
+      <c r="O7" s="3">
         <v>9730150615</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="P7" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="Q4" s="5">
-        <v>9696698</v>
-      </c>
-      <c r="R4" s="6" t="s">
+      <c r="Q7" s="3">
+        <v>9696701</v>
+      </c>
+      <c r="R7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="S7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="T4" s="6" t="s">
+      <c r="T7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="U4" s="6" t="s">
+      <c r="U7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="V4" s="6" t="s">
+      <c r="V7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="W4" s="6" t="s">
+      <c r="W7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="X4" s="6" t="s">
+      <c r="X7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Y7" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="Z4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD4" s="1">
-        <v>5</v>
-      </c>
-      <c r="AE4" s="1"/>
+      <c r="Z7" s="5"/>
+      <c r="AA7" s="5"/>
+      <c r="AB7" s="5"/>
+      <c r="AC7" s="5"/>
+      <c r="AD7" s="5"/>
+      <c r="AE7" s="5"/>
+      <c r="AF7" s="5"/>
+      <c r="AG7" s="5"/>
+      <c r="AH7" s="5"/>
+      <c r="AI7" s="5"/>
+      <c r="AJ7" s="5"/>
+      <c r="AK7" s="5"/>
+      <c r="AL7" s="5"/>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
-        <v>9093</v>
-      </c>
-      <c r="B5" s="6">
-        <v>3217</v>
-      </c>
-      <c r="C5" s="6" t="s">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>9096</v>
+      </c>
+      <c r="B8" s="3">
+        <v>3220</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M8" s="3">
         <v>401202</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N8" s="3">
         <v>91</v>
       </c>
-      <c r="O5" s="5">
+      <c r="O8" s="3">
         <v>9730150615</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="Q5" s="5">
-        <v>9696699</v>
-      </c>
-      <c r="R5" s="6" t="s">
+      <c r="Q8" s="3">
+        <v>9696702</v>
+      </c>
+      <c r="R8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="S5" s="6" t="s">
+      <c r="S8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="T5" s="6" t="s">
+      <c r="T8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="U5" s="6" t="s">
+      <c r="U8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="V5" s="6" t="s">
+      <c r="V8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="W5" s="6" t="s">
+      <c r="W8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="X5" s="6" t="s">
+      <c r="X8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Y5" s="1" t="s">
+      <c r="Y8" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="1"/>
-      <c r="AC5" s="1"/>
-      <c r="AD5" s="1"/>
-      <c r="AE5" s="1"/>
+      <c r="Z8" s="5"/>
+      <c r="AA8" s="5"/>
+      <c r="AB8" s="5"/>
+      <c r="AC8" s="5"/>
+      <c r="AD8" s="5"/>
+      <c r="AE8" s="5"/>
+      <c r="AF8" s="5"/>
+      <c r="AG8" s="5"/>
+      <c r="AH8" s="5"/>
+      <c r="AI8" s="5"/>
+      <c r="AJ8" s="5"/>
+      <c r="AK8" s="5"/>
+      <c r="AL8" s="5"/>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
-        <v>9094</v>
-      </c>
-      <c r="B6" s="6">
-        <v>3218</v>
-      </c>
-      <c r="C6" s="6" t="s">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>9097</v>
+      </c>
+      <c r="B9" s="3">
+        <v>3221</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M9" s="3">
         <v>401202</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N9" s="3">
         <v>91</v>
       </c>
-      <c r="O6" s="5">
+      <c r="O9" s="3">
         <v>9730150615</v>
       </c>
-      <c r="P6" s="4" t="s">
+      <c r="P9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="Q6" s="5">
-        <v>9696700</v>
-      </c>
-      <c r="R6" s="6" t="s">
+      <c r="Q9" s="3">
+        <v>9696703</v>
+      </c>
+      <c r="R9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="S6" s="6" t="s">
+      <c r="S9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="T6" s="6" t="s">
+      <c r="T9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="U6" s="6" t="s">
+      <c r="U9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="V6" s="6" t="s">
+      <c r="V9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="W6" s="6" t="s">
+      <c r="W9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="X6" s="6" t="s">
+      <c r="X9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Y6" s="1" t="s">
+      <c r="Y9" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="1"/>
-      <c r="AC6" s="1"/>
-      <c r="AD6" s="1"/>
-      <c r="AE6" s="1"/>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <v>9095</v>
-      </c>
-      <c r="B7" s="6">
-        <v>3219</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" s="5">
-        <v>401202</v>
-      </c>
-      <c r="N7" s="5">
-        <v>91</v>
-      </c>
-      <c r="O7" s="5">
-        <v>9730150615</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q7" s="5">
-        <v>9696701</v>
-      </c>
-      <c r="R7" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="S7" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="T7" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="U7" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="V7" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="W7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="X7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z7" s="1"/>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="1"/>
-      <c r="AC7" s="1"/>
-      <c r="AD7" s="1"/>
-      <c r="AE7" s="1"/>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
-        <v>9096</v>
-      </c>
-      <c r="B8" s="6">
-        <v>3220</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8" s="5">
-        <v>401202</v>
-      </c>
-      <c r="N8" s="5">
-        <v>91</v>
-      </c>
-      <c r="O8" s="5">
-        <v>9730150615</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q8" s="5">
-        <v>9696702</v>
-      </c>
-      <c r="R8" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="S8" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="T8" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="U8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="V8" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="W8" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="X8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z8" s="1"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="1"/>
-      <c r="AC8" s="1"/>
-      <c r="AD8" s="1"/>
-      <c r="AE8" s="1"/>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
-        <v>9097</v>
-      </c>
-      <c r="B9" s="6">
-        <v>3221</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="5">
-        <v>401202</v>
-      </c>
-      <c r="N9" s="5">
-        <v>91</v>
-      </c>
-      <c r="O9" s="5">
-        <v>9730150615</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q9" s="5">
-        <v>9696703</v>
-      </c>
-      <c r="R9" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="S9" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="T9" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="U9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="V9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="W9" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="X9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z9" s="1"/>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="1"/>
-      <c r="AC9" s="1"/>
-      <c r="AD9" s="1"/>
-      <c r="AE9" s="1"/>
+      <c r="Z9" s="5"/>
+      <c r="AA9" s="5"/>
+      <c r="AB9" s="5"/>
+      <c r="AC9" s="5"/>
+      <c r="AD9" s="5"/>
+      <c r="AE9" s="5"/>
+      <c r="AF9" s="5"/>
+      <c r="AG9" s="5"/>
+      <c r="AH9" s="5"/>
+      <c r="AI9" s="5"/>
+      <c r="AJ9" s="5"/>
+      <c r="AK9" s="5"/>
+      <c r="AL9" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="P2" r:id="rId1" xr:uid="{5A1CE9B2-F66F-4BC4-9BDB-8776A2E46DCB}"/>
     <hyperlink ref="P3" r:id="rId2" xr:uid="{F5F29672-2873-4853-AC97-B448FDA8D01E}"/>
@@ -1411,5 +1549,6 @@
     <hyperlink ref="P9" r:id="rId8" xr:uid="{712F6223-4BE1-41A7-9EA3-545E907E9D57}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>
--- a/Data/ClientOpening.xlsx
+++ b/Data/ClientOpening.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F5E1FA-9D7D-45BA-97A0-118C0E0A11A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68EE5EE3-97FE-4674-9B3B-111515BA9F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" tabRatio="763" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -339,14 +339,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
@@ -760,28 +759,28 @@
       <c r="AE1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AF1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AG1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AH1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AI1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AK1" s="3" t="s">
         <v>59</v>
       </c>
       <c r="AL1" s="5"/>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>9190</v>
       </c>
       <c r="B2" s="3">
@@ -826,7 +825,7 @@
       <c r="O2" s="3">
         <v>9730150615</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="P2" s="7" t="s">
         <v>33</v>
       </c>
       <c r="Q2" s="3">
@@ -887,7 +886,7 @@
       <c r="AL2" s="5"/>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3" s="6">
         <v>9012</v>
       </c>
       <c r="B3" s="3">
@@ -932,7 +931,7 @@
       <c r="O3" s="3">
         <v>9730150615</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="P3" s="7" t="s">
         <v>33</v>
       </c>
       <c r="Q3" s="3">
@@ -987,7 +986,7 @@
       <c r="AL3" s="5"/>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+      <c r="A4" s="6">
         <v>90921</v>
       </c>
       <c r="B4" s="3">
@@ -1032,7 +1031,7 @@
       <c r="O4" s="3">
         <v>9730150615</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="P4" s="7" t="s">
         <v>33</v>
       </c>
       <c r="Q4" s="3">
@@ -1087,7 +1086,7 @@
       <c r="AL4" s="5"/>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="6">
         <v>9093</v>
       </c>
       <c r="B5" s="3">
@@ -1132,7 +1131,7 @@
       <c r="O5" s="3">
         <v>9730150615</v>
       </c>
-      <c r="P5" s="8" t="s">
+      <c r="P5" s="7" t="s">
         <v>33</v>
       </c>
       <c r="Q5" s="3">
@@ -1177,7 +1176,7 @@
       <c r="AL5" s="5"/>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="6">
         <v>9094</v>
       </c>
       <c r="B6" s="3">
@@ -1222,7 +1221,7 @@
       <c r="O6" s="3">
         <v>9730150615</v>
       </c>
-      <c r="P6" s="8" t="s">
+      <c r="P6" s="7" t="s">
         <v>33</v>
       </c>
       <c r="Q6" s="3">
@@ -1267,7 +1266,7 @@
       <c r="AL6" s="5"/>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="6">
         <v>9095</v>
       </c>
       <c r="B7" s="3">
@@ -1312,7 +1311,7 @@
       <c r="O7" s="3">
         <v>9730150615</v>
       </c>
-      <c r="P7" s="8" t="s">
+      <c r="P7" s="7" t="s">
         <v>33</v>
       </c>
       <c r="Q7" s="3">
@@ -1357,7 +1356,7 @@
       <c r="AL7" s="5"/>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="6">
         <v>9096</v>
       </c>
       <c r="B8" s="3">
@@ -1402,7 +1401,7 @@
       <c r="O8" s="3">
         <v>9730150615</v>
       </c>
-      <c r="P8" s="8" t="s">
+      <c r="P8" s="7" t="s">
         <v>33</v>
       </c>
       <c r="Q8" s="3">
@@ -1447,7 +1446,7 @@
       <c r="AL8" s="5"/>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9" s="6">
         <v>9097</v>
       </c>
       <c r="B9" s="3">
@@ -1492,7 +1491,7 @@
       <c r="O9" s="3">
         <v>9730150615</v>
       </c>
-      <c r="P9" s="8" t="s">
+      <c r="P9" s="7" t="s">
         <v>33</v>
       </c>
       <c r="Q9" s="3">

--- a/Data/ClientOpening.xlsx
+++ b/Data/ClientOpening.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68EE5EE3-97FE-4674-9B3B-111515BA9F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55CDE079-A075-40C2-93C3-A4382BDA47A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" tabRatio="763" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" tabRatio="763" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ClientOpening" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="67">
   <si>
     <t>clientid_Num</t>
   </si>
@@ -177,24 +177,12 @@
     <t>INZ000031633</t>
   </si>
   <si>
-    <t>c10092042</t>
-  </si>
-  <si>
     <t>cm_ID</t>
   </si>
   <si>
     <t>netWorth</t>
   </si>
   <si>
-    <t>c10092040</t>
-  </si>
-  <si>
-    <t>TMCM_Linking_CM_42</t>
-  </si>
-  <si>
-    <t>TM_CM_Linking_TM_42</t>
-  </si>
-  <si>
     <t>nominee_name</t>
   </si>
   <si>
@@ -229,6 +217,15 @@
   </si>
   <si>
     <t>nominee_Month+1</t>
+  </si>
+  <si>
+    <t>CM_Prod_Abhi_24</t>
+  </si>
+  <si>
+    <t>TM_Pre_Abhi_24</t>
+  </si>
+  <si>
+    <t>c10092026</t>
   </si>
 </sst>
 </file>
@@ -751,31 +748,31 @@
         <v>46</v>
       </c>
       <c r="AC1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AE1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="AG1" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AH1" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AI1" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="AJ1" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="AL1" s="5"/>
     </row>
@@ -787,7 +784,7 @@
         <v>3214</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>26</v>
@@ -863,10 +860,10 @@
         <v>5</v>
       </c>
       <c r="AE2" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="AF2" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AG2" s="5">
         <v>2007</v>
@@ -878,22 +875,22 @@
         <v>19</v>
       </c>
       <c r="AJ2" s="5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AK2" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="AL2" s="5"/>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>9012</v>
+        <v>9013</v>
       </c>
       <c r="B3" s="3">
-        <v>6421</v>
+        <v>7001</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>42</v>
@@ -971,7 +968,7 @@
         <v>49</v>
       </c>
       <c r="AC3" s="5" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="AD3" s="5">
         <v>5</v>
@@ -987,13 +984,13 @@
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
-        <v>90921</v>
+        <v>9014</v>
       </c>
       <c r="B4" s="3">
-        <v>3216</v>
+        <v>7002</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>43</v>
@@ -1071,7 +1068,7 @@
         <v>49</v>
       </c>
       <c r="AC4" s="5" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="AD4" s="5">
         <v>5</v>
